--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484242_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484242_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.8542</v>
+        <v>-2.7586</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2035</v>
+        <v>1.1629</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.0577</v>
+        <v>-3.9215</v>
       </c>
       <c r="G2" t="n">
         <v>-6.2366</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8446</v>
+        <v>-0.749</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.96</v>
+        <v>-1.0006</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1154</v>
+        <v>0.2516</v>
       </c>
       <c r="V2" t="n">
         <v>3.4457</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.0237</v>
+        <v>-2.8136</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.6495</v>
+        <v>-1.5484</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3741</v>
+        <v>-1.2652</v>
       </c>
       <c r="G3" t="n">
         <v>-1.9105</v>
@@ -688,13 +688,13 @@
         <v>0.1953</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3318</v>
+        <v>-0.1218</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2108</v>
+        <v>-0.1018</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.5978</v>
+        <v>-3.0627</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.3089</v>
+        <v>-2.0461</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2889</v>
+        <v>-1.0166</v>
       </c>
       <c r="G4" t="n">
         <v>-3.3426</v>
@@ -766,13 +766,13 @@
         <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0097</v>
+        <v>-0.4746</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9684</v>
+        <v>-0.7056</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0413</v>
+        <v>0.231</v>
       </c>
       <c r="V4" t="n">
         <v>1.3405</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.7291</v>
+        <v>-3.6123</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5403</v>
+        <v>0.4392</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.2694</v>
+        <v>-4.0515</v>
       </c>
       <c r="G5" t="n">
         <v>0.4876</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8177</v>
+        <v>-0.7009</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4758</v>
+        <v>-0.5769</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3419</v>
+        <v>-0.124</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6642</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.0684</v>
+        <v>-4.0818</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6598</v>
+        <v>1.6192</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.7282</v>
+        <v>-5.701</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4366</v>
@@ -922,13 +922,13 @@
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5816</v>
+        <v>-0.595</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7784</v>
+        <v>-0.819</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1968</v>
+        <v>0.224</v>
       </c>
       <c r="V6" t="n">
         <v>-0.4875</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.566</v>
+        <v>-5.8051</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.095</v>
+        <v>-0.0344</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.471</v>
+        <v>-5.7706</v>
       </c>
       <c r="G7" t="n">
         <v>-4.05</v>
@@ -1000,13 +1000,13 @@
         <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3291</v>
+        <v>-0.5682</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0811</v>
+        <v>-1.0205</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7519</v>
+        <v>0.4524</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2102</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.2503</v>
+        <v>-6.6527</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4101</v>
+        <v>-2.3496</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.8401</v>
+        <v>-4.3031</v>
       </c>
       <c r="G8" t="n">
         <v>-7.8617</v>
@@ -1078,13 +1078,13 @@
         <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0612</v>
+        <v>-0.4636</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0205</v>
+        <v>-0.96</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9594</v>
+        <v>0.4964</v>
       </c>
       <c r="V8" t="n">
         <v>1.6726</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.0895</v>
+        <v>-28.7868</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0599</v>
+        <v>-2.7572</v>
       </c>
       <c r="F9" t="n">
-        <v>-26.0294</v>
+        <v>-26.0295</v>
       </c>
       <c r="G9" t="n">
         <v>-24.3504</v>
@@ -1156,13 +1156,13 @@
         <v>9.767100000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.9757</v>
+        <v>-3.6731</v>
       </c>
       <c r="T9" t="n">
-        <v>-5.4052</v>
+        <v>-5.1025</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4295</v>
+        <v>1.4296</v>
       </c>
       <c r="V9" t="n">
         <v>5.0969</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>9.8931</v>
+        <v>9.6013</v>
       </c>
       <c r="E10" t="n">
-        <v>8.325200000000001</v>
+        <v>8.2241</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5679</v>
+        <v>1.3772</v>
       </c>
       <c r="G10" t="n">
         <v>7.0043</v>
@@ -1234,13 +1234,13 @@
         <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>0.58</v>
+        <v>0.2882</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2943</v>
+        <v>-0.3954</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8742</v>
+        <v>0.6836</v>
       </c>
       <c r="V10" t="n">
         <v>0.9414</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.7351</v>
+        <v>6.7701</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7964</v>
+        <v>2.6953</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9386</v>
+        <v>4.0748</v>
       </c>
       <c r="G11" t="n">
         <v>3.7281</v>
@@ -1312,13 +1312,13 @@
         <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8116</v>
+        <v>0.8467</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0221</v>
+        <v>-0.079</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7895</v>
+        <v>0.9257</v>
       </c>
       <c r="V11" t="n">
         <v>1.2186</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3592</v>
+        <v>5.1809</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5971</v>
+        <v>4.2826</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7621</v>
+        <v>0.8983</v>
       </c>
       <c r="G13" t="n">
         <v>4.3319</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3827</v>
+        <v>1.2044</v>
       </c>
       <c r="T13" t="n">
-        <v>1.728</v>
+        <v>0.4135</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.7909</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9414</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1711</v>
+        <v>2.3073</v>
       </c>
       <c r="E14" t="n">
         <v>2.3578</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1867</v>
+        <v>-0.0505</v>
       </c>
       <c r="G14" t="n">
         <v>1.0136</v>
@@ -1546,13 +1546,13 @@
         <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6301</v>
+        <v>0.7662</v>
       </c>
       <c r="T14" t="n">
         <v>0.2037</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4264</v>
+        <v>0.5625</v>
       </c>
       <c r="V14" t="n">
         <v>0.3321</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3637</v>
+        <v>1.7059</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1282</v>
+        <v>2.6338</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7645</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>5.3015</v>
@@ -1624,13 +1624,13 @@
         <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3477</v>
+        <v>0.6899</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7125</v>
+        <v>-0.2069</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0602</v>
+        <v>0.8968</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5507</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9374</v>
+        <v>1.5519</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7545</v>
+        <v>2.26</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8171</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0.3406</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8022</v>
+        <v>-0.1877</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.773</v>
+        <v>-0.2674</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0292</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5545</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1691</v>
+        <v>-0.2235</v>
       </c>
       <c r="E17" t="n">
         <v>-0.3234</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1543</v>
+        <v>0.0999</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6858</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0693</v>
+        <v>-0.1238</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2337</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1645</v>
+        <v>0.11</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2071</v>
+        <v>-1.1955</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5244</v>
+        <v>1.7266</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7314</v>
+        <v>-2.9221</v>
       </c>
       <c r="G18" t="n">
         <v>0.0174</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0407</v>
+        <v>0.0523</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4704</v>
+        <v>-0.2682</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5111</v>
+        <v>0.3205</v>
       </c>
       <c r="V18" t="n">
         <v>-2.4373</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5815</v>
+        <v>-3.1965</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0775</v>
+        <v>-2.7741</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5041</v>
+        <v>-0.4223</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6265</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7131</v>
+        <v>-0.3281</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6657</v>
+        <v>-0.3624</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0474</v>
+        <v>0.0343</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2186</v>
@@ -1975,7 +1975,7 @@
         <v>26.0295</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0599</v>
+        <v>3.059999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>24.3502</v>
@@ -2014,7 +2014,7 @@
         <v>15.6274</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9758</v>
+        <v>3.9757</v>
       </c>
       <c r="T20" t="n">
         <v>-1.4295</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484242_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484242_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.4875</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.4326</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1554</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.374</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.7647</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,7 @@
       <c r="X9" t="n">
         <v>-3.2142</v>
       </c>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1292,11 @@
       <c r="X10" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1375,11 @@
       <c r="X11" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1458,11 @@
       <c r="X12" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,11 +1956,16 @@
       <c r="X18" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1952,6 +2038,11 @@
       </c>
       <c r="X19" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484242_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2031,6 +2122,7 @@
       <c r="X20" t="n">
         <v>-8.3111</v>
       </c>
+      <c r="Y20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
